--- a/excel/activeskill.xlsx
+++ b/excel/activeskill.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GODOT\Project\BOOOM202604\Booom202604\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBBC0FAA-434D-46B7-AB93-0A9F2079057A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3D9BEA8-D5B2-4CCC-BA75-63DCAC3C2D98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23288" yWindow="720" windowWidth="19965" windowHeight="15120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3450" yWindow="1080" windowWidth="19965" windowHeight="15120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -92,18 +92,6 @@
     <t>res://Art/Icon/askill3.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>在随机明亮位置，生成草地/尸体/废墟各一个</t>
-    </r>
-  </si>
-  <si>
     <t>战前誓师</t>
   </si>
   <si>
@@ -203,6 +191,10 @@
   </si>
   <si>
     <t>选择1个方向，驱散该方向直线2格迷雾</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>在随机明亮位置，生成草地/尸体各一个</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -610,10 +602,10 @@
         <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -624,13 +616,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" t="s">
         <v>17</v>
-      </c>
-      <c r="D5" t="s">
-        <v>18</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -647,13 +639,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" t="s">
         <v>20</v>
-      </c>
-      <c r="D6" t="s">
-        <v>21</v>
       </c>
       <c r="E6">
         <v>4</v>
@@ -670,13 +662,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" t="s">
         <v>23</v>
-      </c>
-      <c r="D7" t="s">
-        <v>24</v>
       </c>
       <c r="E7">
         <v>5</v>
@@ -693,13 +685,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" t="s">
         <v>26</v>
-      </c>
-      <c r="D8" t="s">
-        <v>27</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -713,13 +705,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" t="s">
         <v>29</v>
-      </c>
-      <c r="D9" t="s">
-        <v>30</v>
       </c>
       <c r="E9">
         <v>3</v>
@@ -733,13 +725,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" t="s">
         <v>32</v>
-      </c>
-      <c r="D10" t="s">
-        <v>33</v>
       </c>
       <c r="E10">
         <v>3</v>

--- a/excel/activeskill.xlsx
+++ b/excel/activeskill.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GODOT\Project\BOOOM202604\Booom202604\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3D9BEA8-D5B2-4CCC-BA75-63DCAC3C2D98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A501776-7193-4DCF-ABB3-E18BF6EE76A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3450" yWindow="1080" windowWidth="19965" windowHeight="15120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="19965" windowHeight="15119" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>ID</t>
   </si>
@@ -194,7 +194,31 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>在随机明亮位置，生成草地/尸体各一个</t>
+    <t>艹艹艹</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>res://Art/Icon/askill10.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择1个怪物，将其变为草丛</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>res://Art/Icon/askill11.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>听天由命</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>传送至地图上的随机位置，并驱散相邻的迷雾</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>在随机明亮位置，生成草从/墓地各一个</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -602,7 +626,7 @@
         <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E4">
         <v>4</v>
@@ -625,7 +649,7 @@
         <v>17</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5">
         <v>3</v>
@@ -648,7 +672,7 @@
         <v>20</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F6">
         <v>3</v>
@@ -671,7 +695,7 @@
         <v>23</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F7">
         <v>2</v>
@@ -694,7 +718,7 @@
         <v>26</v>
       </c>
       <c r="E8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -744,10 +768,44 @@
       </c>
     </row>
     <row r="11" spans="1:7" ht="14.25" x14ac:dyDescent="0.45">
-      <c r="C11" s="1"/>
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11">
+        <v>5</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:7" ht="14.25" x14ac:dyDescent="0.45">
-      <c r="C12" s="1"/>
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E12">
+        <v>4</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
